--- a/aec/results/강남/logistic_results.xlsx
+++ b/aec/results/강남/logistic_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>165774941150.4135</v>
+        <v>165774940702.2059</v>
       </c>
       <c r="F10" t="n">
         <v>15.6238</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5.809675456016488e+24</v>
+        <v>5.809675414645115e+24</v>
       </c>
       <c r="F12" t="n">
         <v>32.7998</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>21343455.9162</v>
+        <v>21343455.8898</v>
       </c>
       <c r="F13" t="n">
         <v>8.8864</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>8.427328936678331e+16</v>
+        <v>8.42732889745163e+16</v>
       </c>
       <c r="F16" t="n">
         <v>22.902</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4.917432720699173e+45</v>
+        <v>4.917432649232583e+45</v>
       </c>
       <c r="F17" t="n">
         <v>58.2914</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.380891218526021e+116</v>
+        <v>1.38089121035395e+116</v>
       </c>
       <c r="F18" t="n">
         <v>142.1601</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2.70870036213227e+205</v>
+        <v>2.708700152839503e+205</v>
       </c>
       <c r="F20" t="n">
         <v>247.7577</v>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4.668905437886126e+43</v>
+        <v>4.668905386346648e+43</v>
       </c>
       <c r="F23" t="n">
         <v>55.8541</v>
@@ -1326,7 +1326,7 @@
         <v>14.2873</v>
       </c>
       <c r="C24" t="n">
-        <v>1602779.8732</v>
+        <v>1602779.8727</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2.173192077641967e+37</v>
+        <v>2.173192053178805e+37</v>
       </c>
       <c r="F33" t="n">
         <v>48.1193</v>
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6.467624956431399e+36</v>
+        <v>6.467624886002238e+36</v>
       </c>
       <c r="F34" t="n">
         <v>47.531</v>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>6.509718494360902e+16</v>
+        <v>6.509718465642374e+16</v>
       </c>
       <c r="F35" t="n">
         <v>22.8588</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.169358210293473e+40</v>
+        <v>1.169358196484945e+40</v>
       </c>
       <c r="F36" t="n">
         <v>51.4132</v>
@@ -1724,7 +1724,7 @@
         <v>21.9004</v>
       </c>
       <c r="C38" t="n">
-        <v>3244947973.7528</v>
+        <v>3244947972.3688</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>2.97197638339632e+229</v>
+        <v>2.971975806496113e+229</v>
       </c>
       <c r="F39" t="n">
         <v>276.0284</v>

--- a/aec/results/강남/logistic_results.xlsx
+++ b/aec/results/강남/logistic_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,19 +469,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.0417</v>
+        <v>1.0564</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8317</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3048</v>
+        <v>1.3281</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7219410000000001</v>
+        <v>0.638731</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5049</v>
+        <v>0.5066000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.5758</v>
+        <v>1.5854</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3979</v>
+        <v>1.4024</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7764</v>
+        <v>1.7923</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6234</v>
       </c>
     </row>
     <row r="4">
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5859</v>
+        <v>0.5879</v>
       </c>
       <c r="C4" t="n">
-        <v>0.518</v>
+        <v>0.5191</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6627</v>
+        <v>0.6659</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6469</v>
+        <v>0.6454</v>
       </c>
     </row>
     <row r="5">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.1335</v>
+        <v>1.1175</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0166</v>
+        <v>1.0001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2638</v>
+        <v>1.2486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.024023</v>
+        <v>0.04974</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5446</v>
+        <v>0.541</v>
       </c>
     </row>
     <row r="6">
@@ -557,19 +557,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.1741</v>
+        <v>1.1733</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0462</v>
+        <v>1.0438</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3177</v>
+        <v>1.3188</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006381</v>
+        <v>0.00738</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5462</v>
+        <v>0.5437</v>
       </c>
     </row>
     <row r="7">
@@ -579,19 +579,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.0232</v>
+        <v>1.0288</v>
       </c>
       <c r="C7" t="n">
-        <v>0.917</v>
+        <v>0.9201</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1417</v>
+        <v>1.1503</v>
       </c>
       <c r="E7" t="n">
-        <v>0.681582</v>
+        <v>0.6183070000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4942</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="8">
@@ -601,19 +601,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5859</v>
+        <v>0.5863</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5203</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6599</v>
+        <v>0.6615</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6533</v>
+        <v>0.6526999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LR_χ²=49.654</t>
+          <t>LR_χ²=50.59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.01347</v>
+        <v>0.01076</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5809</v>
       </c>
     </row>
   </sheetData>
@@ -707,25 +707,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.4198</v>
+        <v>-1.4103</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2418</v>
+        <v>0.2441</v>
       </c>
       <c r="D2" t="n">
-        <v>0.044</v>
+        <v>0.0409</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3296</v>
+        <v>1.4553</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8698</v>
+        <v>0.911</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6324</v>
+        <v>-1.5481</v>
       </c>
       <c r="H2" t="n">
-        <v>0.102595</v>
+        <v>0.121597</v>
       </c>
     </row>
     <row r="3">
@@ -735,25 +735,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1574</v>
+        <v>0.141</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1705</v>
+        <v>1.1514</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8612</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5594</v>
+        <v>1.5394</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1464</v>
+        <v>0.1482</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0753</v>
+        <v>0.9516</v>
       </c>
       <c r="H3" t="n">
-        <v>0.282262</v>
+        <v>0.341292</v>
       </c>
     </row>
     <row r="4">
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.598</v>
+        <v>0.6054</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8185</v>
+        <v>1.832</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5782</v>
+        <v>1.5849</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0953</v>
+        <v>2.1176</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0723</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>8.271000000000001</v>
+        <v>8.1892</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -791,25 +791,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7764</v>
+        <v>-0.6352</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4601</v>
+        <v>0.5298</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1523</v>
+        <v>0.1757</v>
       </c>
       <c r="E5" t="n">
-        <v>1.39</v>
+        <v>1.5979</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5642</v>
+        <v>0.5632</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3762</v>
+        <v>-1.1278</v>
       </c>
       <c r="H5" t="n">
-        <v>0.16876</v>
+        <v>0.259399</v>
       </c>
     </row>
     <row r="6">
@@ -819,25 +819,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0149</v>
+        <v>-0.0047</v>
       </c>
       <c r="C6" t="n">
-        <v>1.015</v>
+        <v>0.9954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8005</v>
+        <v>0.7832</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2869</v>
+        <v>1.265</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1211</v>
+        <v>0.1223</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1229</v>
+        <v>-0.0381</v>
       </c>
       <c r="H6" t="n">
-        <v>0.902207</v>
+        <v>0.9696399999999999</v>
       </c>
     </row>
     <row r="7">
@@ -847,25 +847,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0127</v>
+        <v>0.0604</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0128</v>
+        <v>1.0623</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8339</v>
+        <v>0.8761</v>
       </c>
       <c r="E7" t="n">
-        <v>1.23</v>
+        <v>1.2881</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0983</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1279</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.898205</v>
+        <v>0.538936</v>
       </c>
     </row>
     <row r="8">
@@ -875,25 +875,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1762</v>
+        <v>0.2572</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1926</v>
+        <v>1.2932</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9724</v>
+        <v>1.0539</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4627</v>
+        <v>1.5869</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1042</v>
+        <v>0.1044</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6913</v>
+        <v>2.4629</v>
       </c>
       <c r="H8" t="n">
-        <v>0.090777</v>
+        <v>0.01378</v>
       </c>
     </row>
     <row r="9">
@@ -903,25 +903,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.2303</v>
+        <v>-0.3981</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7943</v>
+        <v>0.6716</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2978</v>
+        <v>0.2505</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1183</v>
+        <v>1.8008</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5032</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4602</v>
+        <v>-0.7911</v>
       </c>
       <c r="H9" t="n">
-        <v>0.64538</v>
+        <v>0.428908</v>
       </c>
     </row>
     <row r="10">
@@ -931,25 +931,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-4.7883</v>
+        <v>-4.7368</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0083</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>165774940702.2059</v>
+        <v>217473871818.365</v>
       </c>
       <c r="F10" t="n">
-        <v>15.6238</v>
+        <v>15.7361</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3065</v>
+        <v>-0.301</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7592449999999999</v>
+        <v>0.763402</v>
       </c>
     </row>
     <row r="11">
@@ -959,25 +959,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.7568</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4691</v>
+        <v>0.4717</v>
       </c>
       <c r="D11" t="n">
-        <v>0.028</v>
+        <v>0.0273</v>
       </c>
       <c r="E11" t="n">
-        <v>7.8607</v>
+        <v>8.162699999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4381</v>
+        <v>1.4546</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5263</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.598706</v>
+        <v>0.605434</v>
       </c>
     </row>
     <row r="12">
@@ -987,25 +987,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-7.2648</v>
+        <v>-7.8568</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0007</v>
+        <v>0.0004</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5.809675414645115e+24</v>
+        <v>1.699137147922753e+31</v>
       </c>
       <c r="F12" t="n">
-        <v>32.7998</v>
+        <v>40.6982</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2215</v>
+        <v>-0.1931</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8247100000000001</v>
+        <v>0.84692</v>
       </c>
     </row>
     <row r="13">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5823</v>
+        <v>0.5655</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>21343455.8898</v>
+        <v>115308986.9962</v>
       </c>
       <c r="F13" t="n">
-        <v>8.8864</v>
+        <v>9.762</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0609</v>
+        <v>-0.0584</v>
       </c>
       <c r="H13" t="n">
-        <v>0.951475</v>
+        <v>0.953433</v>
       </c>
     </row>
     <row r="14">
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2851</v>
+        <v>0.1835</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3299</v>
+        <v>1.2015</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1075</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>16.4536</v>
+        <v>16.1555</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2834</v>
+        <v>1.3259</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2222</v>
+        <v>0.1384</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8241810000000001</v>
+        <v>0.8899010000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1071,25 +1071,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0412</v>
+        <v>-0.1139</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9597</v>
+        <v>0.8923</v>
       </c>
       <c r="D15" t="n">
-        <v>0.032</v>
+        <v>0.0287</v>
       </c>
       <c r="E15" t="n">
-        <v>28.7818</v>
+        <v>27.6975</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7352</v>
+        <v>1.7527</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0237</v>
+        <v>-0.065</v>
       </c>
       <c r="H15" t="n">
-        <v>0.981078</v>
+        <v>0.94818</v>
       </c>
     </row>
     <row r="16">
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-5.9142</v>
+        <v>-5.9779</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0027</v>
+        <v>0.0025</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>8.42732889745163e+16</v>
+        <v>5.482749553451126e+17</v>
       </c>
       <c r="F16" t="n">
-        <v>22.902</v>
+        <v>23.89</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2582</v>
+        <v>-0.2502</v>
       </c>
       <c r="H16" t="n">
-        <v>0.796221</v>
+        <v>0.802412</v>
       </c>
     </row>
     <row r="17">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-9.039899999999999</v>
+        <v>-9.153</v>
       </c>
       <c r="C17" t="n">
         <v>0.0001</v>
@@ -1136,16 +1136,16 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4.917432649232583e+45</v>
+        <v>1.304604097987171e+49</v>
       </c>
       <c r="F17" t="n">
-        <v>58.2914</v>
+        <v>62.3713</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1551</v>
+        <v>-0.1467</v>
       </c>
       <c r="H17" t="n">
-        <v>0.876757</v>
+        <v>0.883329</v>
       </c>
     </row>
     <row r="18">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-11.2062</v>
+        <v>-11.9955</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1164,16 +1164,16 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.38089121035395e+116</v>
+        <v>1.95718576571727e+163</v>
       </c>
       <c r="F18" t="n">
-        <v>142.1601</v>
+        <v>197.9569</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0788</v>
+        <v>-0.0606</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9371699999999999</v>
+        <v>0.951681</v>
       </c>
     </row>
     <row r="19">
@@ -1183,25 +1183,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.4864</v>
+        <v>-0.5284</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6148</v>
+        <v>0.5895</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0265</v>
+        <v>0.0241</v>
       </c>
       <c r="E19" t="n">
-        <v>14.2604</v>
+        <v>14.3973</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6041</v>
+        <v>1.6304</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3033</v>
+        <v>-0.3241</v>
       </c>
       <c r="H19" t="n">
-        <v>0.761696</v>
+        <v>0.745842</v>
       </c>
     </row>
     <row r="20">
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-12.5698</v>
+        <v>-13.8853</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1219,17 +1219,19 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
-        <v>2.708700152839503e+205</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>247.7577</v>
+        <v>427.4985</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0507</v>
+        <v>-0.0325</v>
       </c>
       <c r="H20" t="n">
-        <v>0.959537</v>
+        <v>0.974089</v>
       </c>
     </row>
     <row r="21">
@@ -1239,25 +1241,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.3095</v>
+        <v>-0.2883</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7338</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1313</v>
+        <v>0.1242</v>
       </c>
       <c r="E21" t="n">
-        <v>4.1007</v>
+        <v>4.522</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8779</v>
+        <v>0.917</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3525</v>
+        <v>-0.3144</v>
       </c>
       <c r="H21" t="n">
-        <v>0.724446</v>
+        <v>0.753206</v>
       </c>
     </row>
     <row r="22">
@@ -1267,25 +1269,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-1.2601</v>
+        <v>-1.1135</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2836</v>
+        <v>0.3284</v>
       </c>
       <c r="D22" t="n">
-        <v>0.026</v>
+        <v>0.0272</v>
       </c>
       <c r="E22" t="n">
-        <v>3.0944</v>
+        <v>3.9711</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2192</v>
+        <v>1.2717</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0335</v>
+        <v>-0.8756</v>
       </c>
       <c r="H22" t="n">
-        <v>0.301372</v>
+        <v>0.381265</v>
       </c>
     </row>
     <row r="23">
@@ -1295,7 +1297,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-8.9199</v>
+        <v>-9.320499999999999</v>
       </c>
       <c r="C23" t="n">
         <v>0.0001</v>
@@ -1304,16 +1306,16 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4.668905386346648e+43</v>
+        <v>9.083629393035032e+51</v>
       </c>
       <c r="F23" t="n">
-        <v>55.8541</v>
+        <v>65.79649999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1597</v>
+        <v>-0.1417</v>
       </c>
       <c r="H23" t="n">
-        <v>0.873117</v>
+        <v>0.887352</v>
       </c>
     </row>
     <row r="24">
@@ -1323,10 +1325,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14.2873</v>
+        <v>15.0399</v>
       </c>
       <c r="C24" t="n">
-        <v>1602779.8727</v>
+        <v>3402110.5322</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1337,13 +1339,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1092.288</v>
+        <v>1620.4455</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0131</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.989564</v>
+        <v>0.992595</v>
       </c>
     </row>
     <row r="25">
@@ -1353,25 +1355,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3764</v>
+        <v>-0.3897</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6863</v>
+        <v>0.6773</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1227</v>
+        <v>0.1117</v>
       </c>
       <c r="E25" t="n">
-        <v>3.8392</v>
+        <v>4.1082</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8784</v>
+        <v>0.9197</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4285</v>
+        <v>-0.4237</v>
       </c>
       <c r="H25" t="n">
-        <v>0.668291</v>
+        <v>0.671805</v>
       </c>
     </row>
     <row r="26">
@@ -1381,10 +1383,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11.1964</v>
+        <v>11.6828</v>
       </c>
       <c r="C26" t="n">
-        <v>72869.2439</v>
+        <v>118513.8274</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1395,13 +1397,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>360.3914</v>
+        <v>484.9425</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0311</v>
+        <v>0.0241</v>
       </c>
       <c r="H26" t="n">
-        <v>0.975216</v>
+        <v>0.98078</v>
       </c>
     </row>
     <row r="27">
@@ -1411,25 +1413,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.1191</v>
+        <v>1.9836</v>
       </c>
       <c r="C27" t="n">
-        <v>8.323499999999999</v>
+        <v>7.2688</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2504</v>
+        <v>0.218</v>
       </c>
       <c r="E27" t="n">
-        <v>276.7266</v>
+        <v>242.3395</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7878</v>
+        <v>1.7892</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1853</v>
+        <v>1.1087</v>
       </c>
       <c r="H27" t="n">
-        <v>0.235888</v>
+        <v>0.267581</v>
       </c>
     </row>
     <row r="28">
@@ -1439,7 +1441,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-14.8738</v>
+        <v>-16.2072</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1453,13 +1455,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>667.8383</v>
+        <v>1187.4477</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.0223</v>
+        <v>-0.0136</v>
       </c>
       <c r="H28" t="n">
-        <v>0.982231</v>
+        <v>0.98911</v>
       </c>
     </row>
     <row r="29">
@@ -1469,25 +1471,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1078</v>
+        <v>0.0532</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1139</v>
+        <v>1.0546</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2004</v>
+        <v>0.1756</v>
       </c>
       <c r="E29" t="n">
-        <v>6.1908</v>
+        <v>6.3318</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8751</v>
+        <v>0.9145</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1232</v>
+        <v>0.0581</v>
       </c>
       <c r="H29" t="n">
-        <v>0.901933</v>
+        <v>0.953655</v>
       </c>
     </row>
     <row r="30">
@@ -1497,25 +1499,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3348</v>
+        <v>0.3105</v>
       </c>
       <c r="C30" t="n">
-        <v>1.3976</v>
+        <v>1.3641</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1028</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>19.0022</v>
+        <v>19.2611</v>
       </c>
       <c r="F30" t="n">
-        <v>1.3316</v>
+        <v>1.3509</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2514</v>
+        <v>0.2298</v>
       </c>
       <c r="H30" t="n">
-        <v>0.801503</v>
+        <v>0.818225</v>
       </c>
     </row>
     <row r="31">
@@ -1525,25 +1527,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8107</v>
+        <v>-0.8307</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4446</v>
+        <v>0.4357</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0516</v>
+        <v>0.0471</v>
       </c>
       <c r="E31" t="n">
-        <v>3.8293</v>
+        <v>4.028</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0987</v>
+        <v>1.1347</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.7379</v>
+        <v>-0.7321</v>
       </c>
       <c r="H31" t="n">
-        <v>0.460595</v>
+        <v>0.464106</v>
       </c>
     </row>
     <row r="32">
@@ -1553,25 +1555,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2455</v>
+        <v>-0.3334</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7823</v>
+        <v>0.7165</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0401</v>
+        <v>0.0353</v>
       </c>
       <c r="E32" t="n">
-        <v>15.2729</v>
+        <v>14.532</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5161</v>
+        <v>1.5356</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1619</v>
+        <v>-0.2171</v>
       </c>
       <c r="H32" t="n">
-        <v>0.871367</v>
+        <v>0.828138</v>
       </c>
     </row>
     <row r="33">
@@ -1581,25 +1583,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-8.340199999999999</v>
+        <v>-8.835900000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2.173192053178805e+37</v>
+        <v>8.090970313194803e+45</v>
       </c>
       <c r="F33" t="n">
-        <v>48.1193</v>
+        <v>58.4414</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1733</v>
+        <v>-0.1512</v>
       </c>
       <c r="H33" t="n">
-        <v>0.862398</v>
+        <v>0.879823</v>
       </c>
     </row>
     <row r="34">
@@ -1609,7 +1611,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-8.3992</v>
+        <v>-8.588200000000001</v>
       </c>
       <c r="C34" t="n">
         <v>0.0002</v>
@@ -1618,16 +1620,16 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6.467624886002238e+36</v>
+        <v>4.168247429080646e+40</v>
       </c>
       <c r="F34" t="n">
-        <v>47.531</v>
+        <v>52.1026</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1767</v>
+        <v>-0.1648</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8597359999999999</v>
+        <v>0.869075</v>
       </c>
     </row>
     <row r="35">
@@ -1637,25 +1639,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-6.0878</v>
+        <v>-6.4234</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0023</v>
+        <v>0.0016</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>6.509718465642374e+16</v>
+        <v>1.968356071724979e+19</v>
       </c>
       <c r="F35" t="n">
-        <v>22.8588</v>
+        <v>25.9442</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2663</v>
+        <v>-0.2476</v>
       </c>
       <c r="H35" t="n">
-        <v>0.789992</v>
+        <v>0.8044559999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1665,25 +1667,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-8.508100000000001</v>
+        <v>-9.109500000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>1.169358196484945e+40</v>
+        <v>9.852496779102026e+50</v>
       </c>
       <c r="F36" t="n">
-        <v>51.4132</v>
+        <v>64.55549999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1655</v>
+        <v>-0.1411</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8685619999999999</v>
+        <v>0.887782</v>
       </c>
     </row>
     <row r="37">
@@ -1693,25 +1695,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4042</v>
+        <v>0.3797</v>
       </c>
       <c r="C37" t="n">
-        <v>1.4981</v>
+        <v>1.4618</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2688</v>
+        <v>0.2423</v>
       </c>
       <c r="E37" t="n">
-        <v>8.349299999999999</v>
+        <v>8.818899999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.917</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4611</v>
+        <v>0.414</v>
       </c>
       <c r="H37" t="n">
-        <v>0.644716</v>
+        <v>0.678849</v>
       </c>
     </row>
     <row r="38">
@@ -1721,10 +1723,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>21.9004</v>
+        <v>23.8806</v>
       </c>
       <c r="C38" t="n">
-        <v>3244947972.3688</v>
+        <v>23506857561.9763</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -1735,13 +1737,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>13037.9734</v>
+        <v>33203.1824</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0017</v>
+        <v>0.0007</v>
       </c>
       <c r="H38" t="n">
-        <v>0.99866</v>
+        <v>0.999426</v>
       </c>
     </row>
     <row r="39">
@@ -1751,7 +1753,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-12.6245</v>
+        <v>-13.572</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1759,17 +1761,19 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
-        <v>2.971975806496113e+229</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>276.0284</v>
+        <v>418.6559</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0457</v>
+        <v>-0.0324</v>
       </c>
       <c r="H39" t="n">
-        <v>0.963521</v>
+        <v>0.974139</v>
       </c>
     </row>
   </sheetData>
@@ -1810,7 +1814,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1738</v>
+        <v>1673</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1825,7 +1829,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1840,7 +1844,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1855,7 +1859,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7524</v>
+        <v>0.7522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1870,7 +1874,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7279</v>
+        <v>0.7262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1885,7 +1889,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7784</v>
+        <v>0.777</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1911,7 +1915,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2608</v>
+        <v>0.2455</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
@@ -1922,7 +1926,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6835</v>
+        <v>0.7075</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1937,7 +1941,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7055</v>
+        <v>0.6803</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1952,7 +1956,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4228</v>
+        <v>0.4101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1967,7 +1971,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8759</v>
+        <v>0.881</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,7 +1986,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C14" t="inlineStr"/>
     </row>
@@ -1993,7 +1997,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>932</v>
+        <v>866</v>
       </c>
       <c r="C15" t="inlineStr"/>
     </row>
@@ -2004,7 +2008,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C16" t="inlineStr"/>
     </row>
@@ -2015,7 +2019,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -2026,7 +2030,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7.2329</v>
+        <v>4.346</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2041,7 +2045,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.511727</v>
+        <v>0.824635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2069,7 +2073,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2074</v>
+        <v>0.2145</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2084,7 +2088,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1561</v>
+        <v>0.1556</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2099,7 +2103,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1732.23</v>
+        <v>1658.03</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2114,7 +2118,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1939.73</v>
+        <v>1864.08</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
